--- a/pacjenci/ELŻBIETA ŚCIOBŁOWSKA.xlsx
+++ b/pacjenci/ELŻBIETA ŚCIOBŁOWSKA.xlsx
@@ -483,10 +483,14 @@
         </is>
       </c>
       <c r="D2" t="inlineStr"/>
-      <c r="E2" t="inlineStr"/>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>Inne</t>
+        </is>
+      </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Do oceny</t>
+          <t>Aktywna choroba</t>
         </is>
       </c>
       <c r="G2" t="n">
@@ -523,7 +527,11 @@
         </is>
       </c>
       <c r="D3" t="inlineStr"/>
-      <c r="E3" t="inlineStr"/>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>Inne</t>
+        </is>
+      </c>
       <c r="F3" t="inlineStr">
         <is>
           <t>Do oceny</t>
@@ -563,7 +571,11 @@
         </is>
       </c>
       <c r="D4" t="inlineStr"/>
-      <c r="E4" t="inlineStr"/>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>Inne</t>
+        </is>
+      </c>
       <c r="F4" t="inlineStr">
         <is>
           <t>Do oceny</t>

--- a/pacjenci/ELŻBIETA ŚCIOBŁOWSKA.xlsx
+++ b/pacjenci/ELŻBIETA ŚCIOBŁOWSKA.xlsx
@@ -413,191 +413,143 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J4"/>
+  <dimension ref="A1:G4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
+          <t>Nr badania</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
           <t>Data badania</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
-        <is>
-          <t>Nr badania</t>
-        </is>
-      </c>
       <c r="C1" t="inlineStr">
         <is>
-          <t>Etap leczenia</t>
+          <t>Problem kliniczny</t>
         </is>
       </c>
       <c r="D1" t="inlineStr">
         <is>
-          <t>Linia leczenia</t>
+          <t>Zakres badania</t>
         </is>
       </c>
       <c r="E1" t="inlineStr">
         <is>
-          <t>Rozpoznanie</t>
+          <t>Opis badania</t>
         </is>
       </c>
       <c r="F1" t="inlineStr">
         <is>
-          <t>Opis</t>
+          <t>Wnioski</t>
         </is>
       </c>
       <c r="G1" t="inlineStr">
         <is>
           <t>SUVmax</t>
-        </is>
-      </c>
-      <c r="H1" t="inlineStr">
-        <is>
-          <t>Ocena odpowiedzi</t>
-        </is>
-      </c>
-      <c r="I1" t="inlineStr">
-        <is>
-          <t>Deauville</t>
-        </is>
-      </c>
-      <c r="J1" t="inlineStr">
-        <is>
-          <t>Wnioski</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" t="inlineStr">
+      <c r="A2" t="n">
+        <v>1</v>
+      </c>
+      <c r="B2" t="inlineStr">
         <is>
           <t>28.04.2022</t>
         </is>
       </c>
-      <c r="B2" t="n">
-        <v>1</v>
-      </c>
       <c r="C2" t="inlineStr">
         <is>
           <t>Obwodowy chłoniak z komórek T- rozpoznanie z usuniętego prawego migdałka podniebiennego. Ocena zaawansowania klinicznego.</t>
         </is>
       </c>
-      <c r="D2" t="inlineStr"/>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>od szczytu głowy do 1/3 ud. Akwizycję przeprowadzono  po 60 min od podania 18F-FDG. Glikemia: 117 mg%.</t>
+        </is>
+      </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Inne</t>
+          <t>: Aktywny metabolicznie naciek po prawej stronie szyi obejmujący węzły chłonne grupy 2A, 2B, 3 i 4 na łącznym obszarze wielkości ok. 29x46x59 mm wg PET SUV max 10,8. Aktywne metabolicznie węzły chłonne  grupy 4 po stronie prawej, średnicy do 11 mm SUV max do 3,6. Wzmożony metabolizm FDG w lewym migdałku podniebiennym SUV max 4,7. Poza tym fizjologiczny metabolizm FDG w obrębie głowy i szyi. Drobne obwodowe zwapnienie na sklepistości lewego płata czołowego. Hypoplazja zatok czołowych oraz lewej zatoki klinowej. drobne polipowate zgrubienie błony śluzowej w lewej zatoce czołowej. Drobne zgrubienia błony śluzowej oraz niepełna przegroda kostna w zachyłku zębodołowym prawej zatoki szczękowej. Tarczyca miernie powiększona, zwłaszcza w zakresie lewego płata - do kontroli w USG.  Klatka piersiowa i śródpiersie: Fizjologiczny metabolizm FDG w narządach klatki piersiowej i śródpiersia. Zmiany drobnoguzkowo-włókniste w szczycie płuca lewego. Ok. 8mm obwodowy guzek w segm. 2 płuca prawego. Drobne zmiany włókniste obwodowo w segm. 2 i 3 płuca prawego. Niewielkie zmiany włókniste w segm. 5 obu płuc oraz obustronnie nadprzeponowo. Asymetryczne zagęszczenia miąższowe ze zwapnieniami w piersi prawej oraz rozsiane zwapnienia w piersi lewej - wskazana ocena piersi w Mammografii i USG.  Brzuch i miednica: Odcinkowo wzmożony metabolizm FDG w jelitach- w pierwszej kolejności o charakterze czynnościowym. Poza tym fizjologiczny metabolizm FDG w narządach jamy brzusznej i miednicy. Mierne pogrubienie trzonu i proksymalnej części odnogi bocznej nadnercza lewego. Nerka lewa hypoplastyczna lub w części marska.  Układ kostny: Fizjologiczny metabolizm FDG w układzie kostnym objętym badaniem. Zmiany zwyrodnieniowo-wytwórcze kręgosłupa, nasilone w odcinku piersiowym. Esowata skolioza kręgosłupa: nieznaczna prawowypukła w odcinku piersiowym i wydatniejsza lewowypukła w odcinku lędźwiowym, z rotacją kręgów. Wielopoziomowo dyskopatie w odcinku piersiowym kręgosłupa - na poziomie Th5/Th6 ze sklerotyzacją blaszek granicznych i przyległych przednich części trzonów kręgowych - typu Modic 3. Zmiany zwyrodnieniowo-wytwórcze w małych stawach międzykręgowych [nasilone w odcinku lędźwiowym kręgosłupa] oraz w stawach żebrowo-poprzecznych. Os sacrum arcuatum. Zmiany zwyrodnieniowo-wytwórcze w stawach krzyżowo-biodrowych, z obecnością gazu w jamach stawowych oraz ze sklerotyzacją przystawowej struktury kostnej kości krzyżowej i trzonów obu kości biodrowych - wydatną po stronie prawej. Zmiany zwyrodnieniowe w stawach ramiennych, zwłaszcza w prawym.  Inne: Miażdżyca aorty i tt potomnych. Tętniakowate poszerzenie aorty brzusznej w odcinku nadpodziałowym do 36mm. Zmiany miękkotkankowe ze zwapnieniami w tkance podskórnej pośladków - zmiany poiniekcyjne.  Wartości referencyjne: MBPS SUVmax  2,3; Prawy płat wątroby SUVmax do 3,3.</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Aktywna choroba</t>
+          <t>Badaniem PET/CT z18F-FDG uwidoczniono obecność aktywnego metabolicznie procesu chłoniakowego z zajęciem węzłów chłonnych szyi po stronie prawej. Poza tym, jak w opisie powyżej.</t>
         </is>
       </c>
       <c r="G2" t="n">
         <v>10.8</v>
       </c>
-      <c r="H2" t="inlineStr">
-        <is>
-          <t>Baseline</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>Nie dotyczy</t>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>Aktywna metabolicznie choroba przed rozpoczęciem leczenia. Badanie wyjściowe stanowiące punkt odniesienia.</t>
-        </is>
-      </c>
     </row>
     <row r="3">
-      <c r="A3" t="inlineStr">
+      <c r="A3" t="n">
+        <v>2</v>
+      </c>
+      <c r="B3" t="inlineStr">
         <is>
           <t>14.07.2022</t>
         </is>
       </c>
-      <c r="B3" t="n">
-        <v>2</v>
-      </c>
       <c r="C3" t="inlineStr">
         <is>
           <t>Obwodowy chłoniak z komórek T- rozpoznanie z usuniętego prawego migdałka podniebiennego. Chemioterapia CHOP po 2 cyklach (19.05.2022 i 09.06.2022).</t>
         </is>
       </c>
-      <c r="D3" t="inlineStr"/>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>od szczytu głowy do 1/3 ud. Akwizycję przeprowadzono  po 61 min od podania 18F-FDG. Glikemia: 114 mg%.</t>
+        </is>
+      </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Inne</t>
+          <t>: Wzmożony metabolizm FDG w lewym migdałku podniebiennym SUV  max 5,9. Asymetryczne pobudzenie metaboliczne w prawym fałdzie głosowym SUV max 4,1 - do ew. kontroli laryngologicznej.   Poza tym fizjologiczny metabolizm FDG w obrębie głowy i szyi. Drobne obwodowe zwapnienie na sklepistości lewego płata czołowego. Hypoplazja zatok czołowych oraz lewej zatoki klinowej. Drobne polipowate zgrubienie błony śluzowej w lewej zatoce czołowej. Drobne zgrubienia błony śluzowej oraz niepełna przegroda kostna w zachyłku zębodołowym prawej zatoki szczękowej. Tarczyca miernie powiększona, zwłaszcza w zakresie lewego płata - do kontroli w USG.  Klatka piersiowa i śródpiersie: Pobudzenie metaboliczne na przebiegu przełyku, SUV max do 3,6 - czynnościowo?  Poza tym fizjologiczny metabolizm FDG w narządach klatki piersiowej i śródpiersia. Zmiany drobnoguzkowo-włókniste w szczycie płuca lewego. Ok. 8mm obwodowy guzek w segm. 2 płuca prawego. Drobne zmiany włókniste obwodowo w segm. 2 i 3 płuca prawego. Niewielkie zmiany włókniste w segm. 5 obu płuc oraz obustronnie nadprzeponowo. Podejrzenie obecności b. drobnych guzków w płatach górnych z przewagą strony prawej - do weryfikacji w badaniu HRCT. Asymetryczne zagęszczenia miąższowe ze zwapnieniami w piersi prawej oraz rozsiane zwapnienia w piersi lewej - wskazana ocena piersi w Mammografii i USG.  Brzuch i miednica: Odcinkowo wzmożony metabolizm FDG w jelitach- w pierwszej kolejności o charakterze czynnościowym. Poza tym fizjologiczny metabolizm FDG w narządach jamy brzusznej i miednicy. Mierne pogrubienie trzonu i proksymalnej części odnogi bocznej nadnercza lewego. Nerka lewa hypoplastyczna lub w części marska.  Układ kostny: Rozlanie w zmożony metabolizm FDG w układzie kostnym- związany ze stosowanym leczeniem? Poza tym fizjologiczny metabolizm FDG w układzie kostnym objętym badaniem. Zmiany zwyrodnieniowo-wytwórcze kręgosłupa, nasilone w odcinku piersiowym. Esowata skolioza kręgosłupa: nieznaczna prawowypukła w odcinku piersiowym i wydatniejsza lewowypukła w odcinku lędźwiowym, z rotacją kręgów. Wielopoziomowo dyskopatie w odcinku piersiowym kręgosłupa - na poziomie Th5/Th6 ze sklerotyzacją blaszek granicznych i przyległych przednich części trzonów kręgowych - typu Modic 3. Zmiany zwyrodnieniowo-wytwórcze w małych stawach międzykręgowych [nasilone w odcinku lędźwiowym kręgosłupa] oraz w stawach żebrowo-poprzecznych. Os sacrum arcuatum. Zmiany zwyrodnieniowo-wytwórcze w stawach krzyżowo-biodrowych, z obecnością gazu w jamach stawowych oraz ze sklerotyzacją przystawowej struktury kostnej kości krzyżowej i trzonów obu kości biodrowych - wydatną po stronie prawej. Zmiany zwyrodnieniowe w stawach ramiennych, zwłaszcza w prawym.  Inne: Miażdżyca aorty i tt potomnych. Tętniakowate poszerzenie aorty brzusznej w odcinku nadpodziałowym do 36mm. Zmiany miękkotkankowe ze zwapnieniami w tkance podskórnej pośladków - zmiany poiniekcyjne.  Wartości referencyjne: MBPS SUVmax  2,4; Prawy płat wątroby SUVmax do 3,3.</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Do oceny</t>
+          <t>Badaniem PET/CT z 18F-FDG nie uwidoczniono aktywnego metabolicznie procesu w obszarze objętym badaniem -  bardzo dobra odpowiedź na stosowane leczenie. Poza tym, jak w opisie powyżej.</t>
         </is>
       </c>
       <c r="G3" t="n">
         <v>5.9</v>
       </c>
-      <c r="H3" t="inlineStr">
-        <is>
-          <t>SD</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>4 - utrzymujący się wychwyt patologiczny</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>Stabilizacja choroby. Klasyfikacja Lugano: Stable Disease (SD) - stabilizacja choroby. Deauville: 4 - utrzymujący się wychwyt patologiczny.</t>
-        </is>
-      </c>
     </row>
     <row r="4">
-      <c r="A4" t="inlineStr">
+      <c r="A4" t="n">
+        <v>3</v>
+      </c>
+      <c r="B4" t="inlineStr">
         <is>
           <t>27.10.2022</t>
         </is>
       </c>
-      <c r="B4" t="n">
-        <v>3</v>
-      </c>
       <c r="C4" t="inlineStr">
         <is>
           <t>Obwodowy chłoniak z komórek T- rozpoznanie z usuniętego prawego migdałka podniebiennego. Ocena remisji choroby po zakończeniu leczenia.</t>
         </is>
       </c>
-      <c r="D4" t="inlineStr"/>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>od szczytu głowy do 1/3 ud. Akwizycję przeprowadzono  po 61 min od podania 18F-FDG. Glikemia: 114 mg%.</t>
+        </is>
+      </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Inne</t>
+          <t>: Wzmożony metabolizm FDG w lewym migdałku podniebiennym SUV max 3,8  - do kontroli. Asymetryczne pobudzenie metaboliczne w lewej chrząstce nalewkowatej SUV max 4,6 - w pierwszej kolejności czynnościowe.    Poza tym fizjologiczny metabolizm FDG w obrębie głowy i szyi. Drobne obwodowe zwapnienie na sklepistości lewego płata czołowego. Hypoplazja zatok czołowych oraz lewej zatoki klinowej. Drobne polipowate zgrubienie błony śluzowej w lewej zatoce czołowej. Drobne zgrubienia błony śluzowej oraz niepełna przegroda kostna w zachyłku zębodołowym prawej zatoki szczękowej. Tarczyca miernie powiększona, zwłaszcza w zakresie lewego płata - do kontroli w USG.  Klatka piersiowa i śródpiersie: Fizjologiczny metabolizm FDG w narządach klatki piersiowej i śródpiersia. Zmiany drobnoguzkowe w obu płucach z predylekcją do płatów górnych - do weryfikacji w badaniu HRCT. Ok. 8mm obwodowy guzek w segm. 2 płuca prawego. Niewielkie zmiany włókniste w segm. 5 obu płuc oraz obustronnie nadprzeponowo. Asymetryczne zagęszczenia miąższowe ze zwapnieniami w piersi prawej oraz rozsiane zwapnienia w piersi lewej - wskazana ocena piersi w Mammografii i USG. Węzły chłonne pachowe lewe średnicy do 11mm (SUV max 1,6).  Brzuch i miednica: Odcinkowo wzmożony metabolizm FDG w jelitach - w pierwszej kolejności o charakterze czynnościowym. Poza tym fizjologiczny metabolizm FDG w narządach jamy brzusznej i miednicy. Mierne pogrubienie trzonu i proksymalnej części odnogi bocznej nadnercza lewego. Nerka lewa hypoplastyczna lub w części marska.  Układ kostny: Fizjologiczny metabolizm FDG w układzie kostnym objętym badaniem. Zmiany zwyrodnieniowo-wytwórcze kręgosłupa, nasilone w odcinku piersiowym. Esowata skolioza kręgosłupa: nieznaczna prawowypukła w odcinku piersiowym i wydatniejsza lewowypukła w odcinku lędźwiowym, z rotacją kręgów. Wielopoziomowo dyskopatie w odcinku piersiowym kręgosłupa - na poziomie Th5/Th6 ze sklerotyzacją blaszek granicznych i przyległych przednich części trzonów kręgowych - typu Modic 3. Zmiany zwyrodnieniowo-wytwórcze w małych stawach międzykręgowych [nasilone w odcinku lędźwiowym kręgosłupa] oraz w stawach żebrowo-poprzecznych. Os sacrum arcuatum. Zmiany zwyrodnieniowo-wytwórcze w stawach krzyżowo-biodrowych, z obecnością gazu w jamach stawowych oraz ze sklerotyzacją przystawowej struktury kostnej kości krzyżowej i trzonów obu kości biodrowych - wydatną po stronie prawej. Zmiany zwyrodnieniowe w stawach ramiennych, zwłaszcza w prawym.  Inne: Miażdżyca aorty i tt potomnych. Tętniakowate poszerzenie aorty brzusznej w odcinku nadpodziałowym do 37mm. Zmiany miękkotkankowe ze zwapnieniami w tkance podskórnej pośladków - zmiany poiniekcyjne.  Wartości referencyjne: MBPS SUVmax  2,6; Prawy płat wątroby SUVmax do 3,5.</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Do oceny</t>
+          <t>Badaniem PET/CT z 18F-FDG nie uwidoczniono jednoznacznych cech aktywnego metabolicznie procesu w obszarze objętym badaniem. Poza tym, jak w opisie powyżej.</t>
         </is>
       </c>
       <c r="G4" t="n">
         <v>4.6</v>
-      </c>
-      <c r="H4" t="inlineStr">
-        <is>
-          <t>SD</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>4 - utrzymujący się wychwyt patologiczny</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>Stabilizacja choroby. Klasyfikacja Lugano: Stable Disease (SD) - stabilizacja choroby. Deauville: 4 - utrzymujący się wychwyt patologiczny.</t>
-        </is>
       </c>
     </row>
   </sheetData>

--- a/pacjenci/ELŻBIETA ŚCIOBŁOWSKA.xlsx
+++ b/pacjenci/ELŻBIETA ŚCIOBŁOWSKA.xlsx
@@ -413,13 +413,13 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G4"/>
+  <dimension ref="A1:L4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>Nr badania</t>
+          <t>Nr PET</t>
         </is>
       </c>
       <c r="B1" t="inlineStr">
@@ -439,17 +439,42 @@
       </c>
       <c r="E1" t="inlineStr">
         <is>
-          <t>Opis badania</t>
+          <t>Glikemia</t>
         </is>
       </c>
       <c r="F1" t="inlineStr">
         <is>
+          <t>Czas po FDG</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>Głowa i szyja</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>Klatka piersiowa</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
+          <t>Brzuch i miednica</t>
+        </is>
+      </c>
+      <c r="J1" t="inlineStr">
+        <is>
+          <t>Układ kostny</t>
+        </is>
+      </c>
+      <c r="K1" t="inlineStr">
+        <is>
           <t>Wnioski</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
-        <is>
-          <t>SUVmax</t>
+      <c r="L1" t="inlineStr">
+        <is>
+          <t>SUVmax_global</t>
         </is>
       </c>
     </row>
@@ -469,20 +494,45 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>od szczytu głowy do 1/3 ud. Akwizycję przeprowadzono  po 60 min od podania 18F-FDG. Glikemia: 117 mg%.</t>
+          <t>od szczytu głowy do 1/3 ud.</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>: Aktywny metabolicznie naciek po prawej stronie szyi obejmujący węzły chłonne grupy 2A, 2B, 3 i 4 na łącznym obszarze wielkości ok. 29x46x59 mm wg PET SUV max 10,8. Aktywne metabolicznie węzły chłonne  grupy 4 po stronie prawej, średnicy do 11 mm SUV max do 3,6. Wzmożony metabolizm FDG w lewym migdałku podniebiennym SUV max 4,7. Poza tym fizjologiczny metabolizm FDG w obrębie głowy i szyi. Drobne obwodowe zwapnienie na sklepistości lewego płata czołowego. Hypoplazja zatok czołowych oraz lewej zatoki klinowej. drobne polipowate zgrubienie błony śluzowej w lewej zatoce czołowej. Drobne zgrubienia błony śluzowej oraz niepełna przegroda kostna w zachyłku zębodołowym prawej zatoki szczękowej. Tarczyca miernie powiększona, zwłaszcza w zakresie lewego płata - do kontroli w USG.  Klatka piersiowa i śródpiersie: Fizjologiczny metabolizm FDG w narządach klatki piersiowej i śródpiersia. Zmiany drobnoguzkowo-włókniste w szczycie płuca lewego. Ok. 8mm obwodowy guzek w segm. 2 płuca prawego. Drobne zmiany włókniste obwodowo w segm. 2 i 3 płuca prawego. Niewielkie zmiany włókniste w segm. 5 obu płuc oraz obustronnie nadprzeponowo. Asymetryczne zagęszczenia miąższowe ze zwapnieniami w piersi prawej oraz rozsiane zwapnienia w piersi lewej - wskazana ocena piersi w Mammografii i USG.  Brzuch i miednica: Odcinkowo wzmożony metabolizm FDG w jelitach- w pierwszej kolejności o charakterze czynnościowym. Poza tym fizjologiczny metabolizm FDG w narządach jamy brzusznej i miednicy. Mierne pogrubienie trzonu i proksymalnej części odnogi bocznej nadnercza lewego. Nerka lewa hypoplastyczna lub w części marska.  Układ kostny: Fizjologiczny metabolizm FDG w układzie kostnym objętym badaniem. Zmiany zwyrodnieniowo-wytwórcze kręgosłupa, nasilone w odcinku piersiowym. Esowata skolioza kręgosłupa: nieznaczna prawowypukła w odcinku piersiowym i wydatniejsza lewowypukła w odcinku lędźwiowym, z rotacją kręgów. Wielopoziomowo dyskopatie w odcinku piersiowym kręgosłupa - na poziomie Th5/Th6 ze sklerotyzacją blaszek granicznych i przyległych przednich części trzonów kręgowych - typu Modic 3. Zmiany zwyrodnieniowo-wytwórcze w małych stawach międzykręgowych [nasilone w odcinku lędźwiowym kręgosłupa] oraz w stawach żebrowo-poprzecznych. Os sacrum arcuatum. Zmiany zwyrodnieniowo-wytwórcze w stawach krzyżowo-biodrowych, z obecnością gazu w jamach stawowych oraz ze sklerotyzacją przystawowej struktury kostnej kości krzyżowej i trzonów obu kości biodrowych - wydatną po stronie prawej. Zmiany zwyrodnieniowe w stawach ramiennych, zwłaszcza w prawym.  Inne: Miażdżyca aorty i tt potomnych. Tętniakowate poszerzenie aorty brzusznej w odcinku nadpodziałowym do 36mm. Zmiany miękkotkankowe ze zwapnieniami w tkance podskórnej pośladków - zmiany poiniekcyjne.  Wartości referencyjne: MBPS SUVmax  2,3; Prawy płat wątroby SUVmax do 3,3.</t>
+          <t>117</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
+          <t>60</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>Aktywny metabolicznie naciek po prawej stronie szyi obejmujący węzły chłonne grupy 2A, 2B, 3 i 4 na łącznym obszarze wielkości ok. 29x46x59 mm wg PET SUV max 10,8. Aktywne metabolicznie węzły chłonne  grupy 4 po stronie prawej, średnicy do 11 mm SUV max do 3,6. Wzmożony metabolizm FDG w lewym migdałku podniebiennym SUV max 4,7. Poza tym fizjologiczny metabolizm FDG w obrębie głowy i szyi. Drobne obwodowe zwapnienie na sklepistości lewego płata czołowego. Hypoplazja zatok czołowych oraz lewej zatoki klinowej. drobne polipowate zgrubienie błony śluzowej w lewej zatoce czołowej. Drobne zgrubienia błony śluzowej oraz niepełna przegroda kostna w zachyłku zębodołowym prawej zatoki szczękowej. Tarczyca miernie powiększona, zwłaszcza w zakresie lewego płata - do kontroli w USG.</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>Fizjologiczny metabolizm FDG w narządach klatki piersiowej i śródpiersia. Zmiany drobnoguzkowo-włókniste w szczycie płuca lewego. Ok. 8mm obwodowy guzek w segm. 2 płuca prawego. Drobne zmiany włókniste obwodowo w segm. 2 i 3 płuca prawego. Niewielkie zmiany włókniste w segm. 5 obu płuc oraz obustronnie nadprzeponowo. Asymetryczne zagęszczenia miąższowe ze zwapnieniami w piersi prawej oraz rozsiane zwapnienia w piersi lewej - wskazana ocena piersi w Mammografii i USG.</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>Odcinkowo wzmożony metabolizm FDG w jelitach- w pierwszej kolejności o charakterze czynnościowym. Poza tym fizjologiczny metabolizm FDG w narządach jamy brzusznej i miednicy. Mierne pogrubienie trzonu i proksymalnej części odnogi bocznej nadnercza lewego. Nerka lewa hypoplastyczna lub w części marska.</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>Fizjologiczny metabolizm FDG w układzie kostnym objętym badaniem. Zmiany zwyrodnieniowo-wytwórcze kręgosłupa, nasilone w odcinku piersiowym. Esowata skolioza kręgosłupa: nieznaczna prawowypukła w odcinku piersiowym i wydatniejsza lewowypukła w odcinku lędźwiowym, z rotacją kręgów. Wielopoziomowo dyskopatie w odcinku piersiowym kręgosłupa - na poziomie Th5/Th6 ze sklerotyzacją blaszek granicznych i przyległych przednich części trzonów kręgowych - typu Modic 3. Zmiany zwyrodnieniowo-wytwórcze w małych stawach międzykręgowych [nasilone w odcinku lędźwiowym kręgosłupa] oraz w stawach żebrowo-poprzecznych. Os sacrum arcuatum. Zmiany zwyrodnieniowo-wytwórcze w stawach krzyżowo-biodrowych, z obecnością gazu w jamach stawowych oraz ze sklerotyzacją przystawowej struktury kostnej kości krzyżowej i trzonów obu kości biodrowych - wydatną po stronie prawej. Zmiany zwyrodnieniowe w stawach ramiennych, zwłaszcza w prawym.  Inne: Miażdżyca aorty i tt potomnych. Tętniakowate poszerzenie aorty brzusznej w odcinku nadpodziałowym do 36mm. Zmiany miękkotkankowe ze zwapnieniami w tkance podskórnej pośladków - zmiany poiniekcyjne.</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
           <t>Badaniem PET/CT z18F-FDG uwidoczniono obecność aktywnego metabolicznie procesu chłoniakowego z zajęciem węzłów chłonnych szyi po stronie prawej. Poza tym, jak w opisie powyżej.</t>
         </is>
       </c>
-      <c r="G2" t="n">
+      <c r="L2" t="n">
         <v>10.8</v>
       </c>
     </row>
@@ -502,20 +552,45 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>od szczytu głowy do 1/3 ud. Akwizycję przeprowadzono  po 61 min od podania 18F-FDG. Glikemia: 114 mg%.</t>
+          <t>od szczytu głowy do 1/3 ud.</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>: Wzmożony metabolizm FDG w lewym migdałku podniebiennym SUV  max 5,9. Asymetryczne pobudzenie metaboliczne w prawym fałdzie głosowym SUV max 4,1 - do ew. kontroli laryngologicznej.   Poza tym fizjologiczny metabolizm FDG w obrębie głowy i szyi. Drobne obwodowe zwapnienie na sklepistości lewego płata czołowego. Hypoplazja zatok czołowych oraz lewej zatoki klinowej. Drobne polipowate zgrubienie błony śluzowej w lewej zatoce czołowej. Drobne zgrubienia błony śluzowej oraz niepełna przegroda kostna w zachyłku zębodołowym prawej zatoki szczękowej. Tarczyca miernie powiększona, zwłaszcza w zakresie lewego płata - do kontroli w USG.  Klatka piersiowa i śródpiersie: Pobudzenie metaboliczne na przebiegu przełyku, SUV max do 3,6 - czynnościowo?  Poza tym fizjologiczny metabolizm FDG w narządach klatki piersiowej i śródpiersia. Zmiany drobnoguzkowo-włókniste w szczycie płuca lewego. Ok. 8mm obwodowy guzek w segm. 2 płuca prawego. Drobne zmiany włókniste obwodowo w segm. 2 i 3 płuca prawego. Niewielkie zmiany włókniste w segm. 5 obu płuc oraz obustronnie nadprzeponowo. Podejrzenie obecności b. drobnych guzków w płatach górnych z przewagą strony prawej - do weryfikacji w badaniu HRCT. Asymetryczne zagęszczenia miąższowe ze zwapnieniami w piersi prawej oraz rozsiane zwapnienia w piersi lewej - wskazana ocena piersi w Mammografii i USG.  Brzuch i miednica: Odcinkowo wzmożony metabolizm FDG w jelitach- w pierwszej kolejności o charakterze czynnościowym. Poza tym fizjologiczny metabolizm FDG w narządach jamy brzusznej i miednicy. Mierne pogrubienie trzonu i proksymalnej części odnogi bocznej nadnercza lewego. Nerka lewa hypoplastyczna lub w części marska.  Układ kostny: Rozlanie w zmożony metabolizm FDG w układzie kostnym- związany ze stosowanym leczeniem? Poza tym fizjologiczny metabolizm FDG w układzie kostnym objętym badaniem. Zmiany zwyrodnieniowo-wytwórcze kręgosłupa, nasilone w odcinku piersiowym. Esowata skolioza kręgosłupa: nieznaczna prawowypukła w odcinku piersiowym i wydatniejsza lewowypukła w odcinku lędźwiowym, z rotacją kręgów. Wielopoziomowo dyskopatie w odcinku piersiowym kręgosłupa - na poziomie Th5/Th6 ze sklerotyzacją blaszek granicznych i przyległych przednich części trzonów kręgowych - typu Modic 3. Zmiany zwyrodnieniowo-wytwórcze w małych stawach międzykręgowych [nasilone w odcinku lędźwiowym kręgosłupa] oraz w stawach żebrowo-poprzecznych. Os sacrum arcuatum. Zmiany zwyrodnieniowo-wytwórcze w stawach krzyżowo-biodrowych, z obecnością gazu w jamach stawowych oraz ze sklerotyzacją przystawowej struktury kostnej kości krzyżowej i trzonów obu kości biodrowych - wydatną po stronie prawej. Zmiany zwyrodnieniowe w stawach ramiennych, zwłaszcza w prawym.  Inne: Miażdżyca aorty i tt potomnych. Tętniakowate poszerzenie aorty brzusznej w odcinku nadpodziałowym do 36mm. Zmiany miękkotkankowe ze zwapnieniami w tkance podskórnej pośladków - zmiany poiniekcyjne.  Wartości referencyjne: MBPS SUVmax  2,4; Prawy płat wątroby SUVmax do 3,3.</t>
+          <t>114</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
+          <t>61</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>Wzmożony metabolizm FDG w lewym migdałku podniebiennym SUV  max 5,9. Asymetryczne pobudzenie metaboliczne w prawym fałdzie głosowym SUV max 4,1 - do ew. kontroli laryngologicznej.   Poza tym fizjologiczny metabolizm FDG w obrębie głowy i szyi. Drobne obwodowe zwapnienie na sklepistości lewego płata czołowego. Hypoplazja zatok czołowych oraz lewej zatoki klinowej. Drobne polipowate zgrubienie błony śluzowej w lewej zatoce czołowej. Drobne zgrubienia błony śluzowej oraz niepełna przegroda kostna w zachyłku zębodołowym prawej zatoki szczękowej. Tarczyca miernie powiększona, zwłaszcza w zakresie lewego płata - do kontroli w USG.</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>Pobudzenie metaboliczne na przebiegu przełyku, SUV max do 3,6 - czynnościowo?  Poza tym fizjologiczny metabolizm FDG w narządach klatki piersiowej i śródpiersia. Zmiany drobnoguzkowo-włókniste w szczycie płuca lewego. Ok. 8mm obwodowy guzek w segm. 2 płuca prawego. Drobne zmiany włókniste obwodowo w segm. 2 i 3 płuca prawego. Niewielkie zmiany włókniste w segm. 5 obu płuc oraz obustronnie nadprzeponowo. Podejrzenie obecności b. drobnych guzków w płatach górnych z przewagą strony prawej - do weryfikacji w badaniu HRCT. Asymetryczne zagęszczenia miąższowe ze zwapnieniami w piersi prawej oraz rozsiane zwapnienia w piersi lewej - wskazana ocena piersi w Mammografii i USG.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>Odcinkowo wzmożony metabolizm FDG w jelitach- w pierwszej kolejności o charakterze czynnościowym. Poza tym fizjologiczny metabolizm FDG w narządach jamy brzusznej i miednicy. Mierne pogrubienie trzonu i proksymalnej części odnogi bocznej nadnercza lewego. Nerka lewa hypoplastyczna lub w części marska.</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>Rozlanie w zmożony metabolizm FDG w układzie kostnym- związany ze stosowanym leczeniem? Poza tym fizjologiczny metabolizm FDG w układzie kostnym objętym badaniem. Zmiany zwyrodnieniowo-wytwórcze kręgosłupa, nasilone w odcinku piersiowym. Esowata skolioza kręgosłupa: nieznaczna prawowypukła w odcinku piersiowym i wydatniejsza lewowypukła w odcinku lędźwiowym, z rotacją kręgów. Wielopoziomowo dyskopatie w odcinku piersiowym kręgosłupa - na poziomie Th5/Th6 ze sklerotyzacją blaszek granicznych i przyległych przednich części trzonów kręgowych - typu Modic 3. Zmiany zwyrodnieniowo-wytwórcze w małych stawach międzykręgowych [nasilone w odcinku lędźwiowym kręgosłupa] oraz w stawach żebrowo-poprzecznych. Os sacrum arcuatum. Zmiany zwyrodnieniowo-wytwórcze w stawach krzyżowo-biodrowych, z obecnością gazu w jamach stawowych oraz ze sklerotyzacją przystawowej struktury kostnej kości krzyżowej i trzonów obu kości biodrowych - wydatną po stronie prawej. Zmiany zwyrodnieniowe w stawach ramiennych, zwłaszcza w prawym.  Inne: Miażdżyca aorty i tt potomnych. Tętniakowate poszerzenie aorty brzusznej w odcinku nadpodziałowym do 36mm. Zmiany miękkotkankowe ze zwapnieniami w tkance podskórnej pośladków - zmiany poiniekcyjne.</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
           <t>Badaniem PET/CT z 18F-FDG nie uwidoczniono aktywnego metabolicznie procesu w obszarze objętym badaniem -  bardzo dobra odpowiedź na stosowane leczenie. Poza tym, jak w opisie powyżej.</t>
         </is>
       </c>
-      <c r="G3" t="n">
+      <c r="L3" t="n">
         <v>5.9</v>
       </c>
     </row>
@@ -535,20 +610,45 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>od szczytu głowy do 1/3 ud. Akwizycję przeprowadzono  po 61 min od podania 18F-FDG. Glikemia: 114 mg%.</t>
+          <t>od szczytu głowy do 1/3 ud.</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>: Wzmożony metabolizm FDG w lewym migdałku podniebiennym SUV max 3,8  - do kontroli. Asymetryczne pobudzenie metaboliczne w lewej chrząstce nalewkowatej SUV max 4,6 - w pierwszej kolejności czynnościowe.    Poza tym fizjologiczny metabolizm FDG w obrębie głowy i szyi. Drobne obwodowe zwapnienie na sklepistości lewego płata czołowego. Hypoplazja zatok czołowych oraz lewej zatoki klinowej. Drobne polipowate zgrubienie błony śluzowej w lewej zatoce czołowej. Drobne zgrubienia błony śluzowej oraz niepełna przegroda kostna w zachyłku zębodołowym prawej zatoki szczękowej. Tarczyca miernie powiększona, zwłaszcza w zakresie lewego płata - do kontroli w USG.  Klatka piersiowa i śródpiersie: Fizjologiczny metabolizm FDG w narządach klatki piersiowej i śródpiersia. Zmiany drobnoguzkowe w obu płucach z predylekcją do płatów górnych - do weryfikacji w badaniu HRCT. Ok. 8mm obwodowy guzek w segm. 2 płuca prawego. Niewielkie zmiany włókniste w segm. 5 obu płuc oraz obustronnie nadprzeponowo. Asymetryczne zagęszczenia miąższowe ze zwapnieniami w piersi prawej oraz rozsiane zwapnienia w piersi lewej - wskazana ocena piersi w Mammografii i USG. Węzły chłonne pachowe lewe średnicy do 11mm (SUV max 1,6).  Brzuch i miednica: Odcinkowo wzmożony metabolizm FDG w jelitach - w pierwszej kolejności o charakterze czynnościowym. Poza tym fizjologiczny metabolizm FDG w narządach jamy brzusznej i miednicy. Mierne pogrubienie trzonu i proksymalnej części odnogi bocznej nadnercza lewego. Nerka lewa hypoplastyczna lub w części marska.  Układ kostny: Fizjologiczny metabolizm FDG w układzie kostnym objętym badaniem. Zmiany zwyrodnieniowo-wytwórcze kręgosłupa, nasilone w odcinku piersiowym. Esowata skolioza kręgosłupa: nieznaczna prawowypukła w odcinku piersiowym i wydatniejsza lewowypukła w odcinku lędźwiowym, z rotacją kręgów. Wielopoziomowo dyskopatie w odcinku piersiowym kręgosłupa - na poziomie Th5/Th6 ze sklerotyzacją blaszek granicznych i przyległych przednich części trzonów kręgowych - typu Modic 3. Zmiany zwyrodnieniowo-wytwórcze w małych stawach międzykręgowych [nasilone w odcinku lędźwiowym kręgosłupa] oraz w stawach żebrowo-poprzecznych. Os sacrum arcuatum. Zmiany zwyrodnieniowo-wytwórcze w stawach krzyżowo-biodrowych, z obecnością gazu w jamach stawowych oraz ze sklerotyzacją przystawowej struktury kostnej kości krzyżowej i trzonów obu kości biodrowych - wydatną po stronie prawej. Zmiany zwyrodnieniowe w stawach ramiennych, zwłaszcza w prawym.  Inne: Miażdżyca aorty i tt potomnych. Tętniakowate poszerzenie aorty brzusznej w odcinku nadpodziałowym do 37mm. Zmiany miękkotkankowe ze zwapnieniami w tkance podskórnej pośladków - zmiany poiniekcyjne.  Wartości referencyjne: MBPS SUVmax  2,6; Prawy płat wątroby SUVmax do 3,5.</t>
+          <t>114</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
+          <t>61</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Wzmożony metabolizm FDG w lewym migdałku podniebiennym SUV max 3,8  - do kontroli. Asymetryczne pobudzenie metaboliczne w lewej chrząstce nalewkowatej SUV max 4,6 - w pierwszej kolejności czynnościowe.    Poza tym fizjologiczny metabolizm FDG w obrębie głowy i szyi. Drobne obwodowe zwapnienie na sklepistości lewego płata czołowego. Hypoplazja zatok czołowych oraz lewej zatoki klinowej. Drobne polipowate zgrubienie błony śluzowej w lewej zatoce czołowej. Drobne zgrubienia błony śluzowej oraz niepełna przegroda kostna w zachyłku zębodołowym prawej zatoki szczękowej. Tarczyca miernie powiększona, zwłaszcza w zakresie lewego płata - do kontroli w USG.</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>Fizjologiczny metabolizm FDG w narządach klatki piersiowej i śródpiersia. Zmiany drobnoguzkowe w obu płucach z predylekcją do płatów górnych - do weryfikacji w badaniu HRCT. Ok. 8mm obwodowy guzek w segm. 2 płuca prawego. Niewielkie zmiany włókniste w segm. 5 obu płuc oraz obustronnie nadprzeponowo. Asymetryczne zagęszczenia miąższowe ze zwapnieniami w piersi prawej oraz rozsiane zwapnienia w piersi lewej - wskazana ocena piersi w Mammografii i USG. Węzły chłonne pachowe lewe średnicy do 11mm (SUV max 1,6).</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>Odcinkowo wzmożony metabolizm FDG w jelitach - w pierwszej kolejności o charakterze czynnościowym. Poza tym fizjologiczny metabolizm FDG w narządach jamy brzusznej i miednicy. Mierne pogrubienie trzonu i proksymalnej części odnogi bocznej nadnercza lewego. Nerka lewa hypoplastyczna lub w części marska.</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>Fizjologiczny metabolizm FDG w układzie kostnym objętym badaniem. Zmiany zwyrodnieniowo-wytwórcze kręgosłupa, nasilone w odcinku piersiowym. Esowata skolioza kręgosłupa: nieznaczna prawowypukła w odcinku piersiowym i wydatniejsza lewowypukła w odcinku lędźwiowym, z rotacją kręgów. Wielopoziomowo dyskopatie w odcinku piersiowym kręgosłupa - na poziomie Th5/Th6 ze sklerotyzacją blaszek granicznych i przyległych przednich części trzonów kręgowych - typu Modic 3. Zmiany zwyrodnieniowo-wytwórcze w małych stawach międzykręgowych [nasilone w odcinku lędźwiowym kręgosłupa] oraz w stawach żebrowo-poprzecznych. Os sacrum arcuatum. Zmiany zwyrodnieniowo-wytwórcze w stawach krzyżowo-biodrowych, z obecnością gazu w jamach stawowych oraz ze sklerotyzacją przystawowej struktury kostnej kości krzyżowej i trzonów obu kości biodrowych - wydatną po stronie prawej. Zmiany zwyrodnieniowe w stawach ramiennych, zwłaszcza w prawym.  Inne: Miażdżyca aorty i tt potomnych. Tętniakowate poszerzenie aorty brzusznej w odcinku nadpodziałowym do 37mm. Zmiany miękkotkankowe ze zwapnieniami w tkance podskórnej pośladków - zmiany poiniekcyjne.</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
           <t>Badaniem PET/CT z 18F-FDG nie uwidoczniono jednoznacznych cech aktywnego metabolicznie procesu w obszarze objętym badaniem. Poza tym, jak w opisie powyżej.</t>
         </is>
       </c>
-      <c r="G4" t="n">
+      <c r="L4" t="n">
         <v>4.6</v>
       </c>
     </row>
